--- a/docs/sm/validacao_face/questionario.xlsx
+++ b/docs/sm/validacao_face/questionario.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="848">
   <si>
     <t>Operação Atlântico Sul — Segurança Marítima</t>
   </si>
@@ -1875,6 +1875,9 @@
   </si>
   <si>
     <t>Risco ambiental em Rotina, em % do risco em Crise</t>
+  </si>
+  <si>
+    <t>% do risco em Crise</t>
   </si>
   <si>
     <t>J3.6</t>
@@ -10849,7 +10852,7 @@
         <v>50</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>41</v>
+        <v>619</v>
       </c>
       <c r="G313" s="12"/>
       <c r="H313" s="12"/>
@@ -10859,7 +10862,7 @@
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" s="11" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B314" s="11" t="s">
         <v>582</v>
@@ -10868,13 +10871,13 @@
         <v>44</v>
       </c>
       <c r="D314" s="11" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E314" s="11">
         <v>75</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>41</v>
+        <v>619</v>
       </c>
       <c r="G314" s="12"/>
       <c r="H314" s="12"/>
@@ -10884,7 +10887,7 @@
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B315" s="11" t="s">
         <v>582</v>
@@ -10893,13 +10896,13 @@
         <v>44</v>
       </c>
       <c r="D315" s="11" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E315" s="11">
         <v>100</v>
       </c>
       <c r="F315" s="11" t="s">
-        <v>41</v>
+        <v>619</v>
       </c>
       <c r="G315" s="12"/>
       <c r="H315" s="12"/>
@@ -10909,7 +10912,7 @@
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" s="11" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B316" s="11" t="s">
         <v>582</v>
@@ -10918,13 +10921,13 @@
         <v>44</v>
       </c>
       <c r="D316" s="11" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E316" s="11">
         <v>150</v>
       </c>
       <c r="F316" s="11" t="s">
-        <v>41</v>
+        <v>619</v>
       </c>
       <c r="G316" s="12"/>
       <c r="H316" s="12"/>
@@ -10934,16 +10937,16 @@
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" s="10" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B317" s="10" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C317" s="10" t="s">
         <v>182</v>
       </c>
       <c r="D317" s="10" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E317" s="10"/>
       <c r="F317" s="10"/>
@@ -10955,16 +10958,16 @@
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C318" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D318" s="11" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E318" s="11">
         <v>1</v>
@@ -10980,16 +10983,16 @@
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" s="11" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B319" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C319" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D319" s="11" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E319" s="11">
         <v>3</v>
@@ -11005,16 +11008,16 @@
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" s="11" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B320" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C320" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D320" s="11" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E320" s="11">
         <v>2</v>
@@ -11030,16 +11033,16 @@
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" s="11" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B321" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C321" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D321" s="11" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E321" s="11">
         <v>5</v>
@@ -11055,16 +11058,16 @@
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" s="11" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B322" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C322" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D322" s="11" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E322" s="11">
         <v>1</v>
@@ -11080,16 +11083,16 @@
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" s="11" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B323" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C323" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D323" s="11" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E323" s="11">
         <v>4</v>
@@ -11105,16 +11108,16 @@
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" s="11" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B324" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C324" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D324" s="11" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E324" s="11">
         <v>2</v>
@@ -11130,16 +11133,16 @@
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A325" s="11" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B325" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C325" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D325" s="11" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E325" s="11">
         <v>6</v>
@@ -11155,16 +11158,16 @@
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A326" s="11" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B326" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C326" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D326" s="11" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E326" s="11">
         <v>1</v>
@@ -11180,16 +11183,16 @@
     </row>
     <row r="327" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A327" s="11" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B327" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C327" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D327" s="11" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E327" s="11">
         <v>3</v>
@@ -11205,16 +11208,16 @@
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A328" s="11" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B328" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C328" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D328" s="11" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E328" s="11">
         <v>3</v>
@@ -11230,16 +11233,16 @@
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A329" s="11" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B329" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C329" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D329" s="11" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E329" s="11">
         <v>6</v>
@@ -11255,16 +11258,16 @@
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A330" s="11" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B330" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C330" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D330" s="11" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E330" s="11">
         <v>0</v>
@@ -11280,16 +11283,16 @@
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A331" s="11" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B331" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C331" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D331" s="11" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="E331" s="11">
         <v>2</v>
@@ -11305,16 +11308,16 @@
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A332" s="11" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B332" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C332" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D332" s="11" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E332" s="11">
         <v>1</v>
@@ -11330,16 +11333,16 @@
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A333" s="11" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B333" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C333" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D333" s="11" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E333" s="11">
         <v>3</v>
@@ -11355,16 +11358,16 @@
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A334" s="11" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B334" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C334" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D334" s="11" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E334" s="11">
         <v>1</v>
@@ -11380,16 +11383,16 @@
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A335" s="11" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C335" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D335" s="11" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E335" s="11">
         <v>3</v>
@@ -11405,16 +11408,16 @@
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A336" s="11" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C336" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D336" s="11" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E336" s="11">
         <v>2</v>
@@ -11430,16 +11433,16 @@
     </row>
     <row r="337" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A337" s="11" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B337" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C337" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D337" s="11" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E337" s="11">
         <v>5</v>
@@ -11455,16 +11458,16 @@
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" s="10" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B338" s="10" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C338" s="10" t="s">
         <v>182</v>
       </c>
       <c r="D338" s="10" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E338" s="10"/>
       <c r="F338" s="10"/>
@@ -11476,22 +11479,22 @@
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" s="11" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B339" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C339" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D339" s="11" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E339" s="11">
         <v>3</v>
       </c>
       <c r="F339" s="11" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G339" s="12"/>
       <c r="H339" s="12"/>
@@ -11501,22 +11504,22 @@
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" s="11" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C340" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D340" s="11" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E340" s="11">
         <v>8</v>
       </c>
       <c r="F340" s="11" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G340" s="12"/>
       <c r="H340" s="12"/>
@@ -11526,16 +11529,16 @@
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" s="11" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B341" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C341" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D341" s="11" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E341" s="11">
         <v>50</v>
@@ -11551,22 +11554,22 @@
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" s="11" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B342" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C342" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D342" s="11" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E342" s="11">
         <v>30</v>
       </c>
       <c r="F342" s="11" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="G342" s="12"/>
       <c r="H342" s="12"/>
@@ -11576,16 +11579,16 @@
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A343" s="11" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C343" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D343" s="11" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E343" s="11">
         <v>1</v>
@@ -11601,16 +11604,16 @@
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" s="11" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C344" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D344" s="11" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E344" s="11">
         <v>2</v>
@@ -11626,16 +11629,16 @@
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A345" s="11" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B345" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C345" s="11" t="s">
         <v>182</v>
       </c>
       <c r="D345" s="11" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E345" s="11">
         <v>20</v>
@@ -11651,16 +11654,16 @@
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A346" s="10" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C346" s="10" t="s">
         <v>44</v>
       </c>
       <c r="D346" s="10" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E346" s="10"/>
       <c r="F346" s="10"/>
@@ -11672,22 +11675,22 @@
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" s="11" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B347" s="11" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C347" s="11" t="s">
         <v>44</v>
       </c>
       <c r="D347" s="11" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E347" s="11">
         <v>4</v>
       </c>
       <c r="F347" s="11" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G347" s="12"/>
       <c r="H347" s="12"/>
@@ -11697,22 +11700,22 @@
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" s="11" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C348" s="11" t="s">
         <v>44</v>
       </c>
       <c r="D348" s="11" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E348" s="11">
         <v>2</v>
       </c>
       <c r="F348" s="11" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G348" s="12"/>
       <c r="H348" s="12"/>
@@ -11722,22 +11725,22 @@
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" s="11" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C349" s="11" t="s">
         <v>44</v>
       </c>
       <c r="D349" s="11" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E349" s="11">
         <v>2</v>
       </c>
       <c r="F349" s="11" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G349" s="12"/>
       <c r="H349" s="12"/>
@@ -11747,16 +11750,16 @@
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" s="11" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B350" s="11" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C350" s="11" t="s">
         <v>44</v>
       </c>
       <c r="D350" s="11" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E350" s="11">
         <v>1</v>
@@ -11772,16 +11775,16 @@
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" s="11" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C351" s="11" t="s">
         <v>44</v>
       </c>
       <c r="D351" s="11" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E351" s="11">
         <v>50</v>
@@ -11797,16 +11800,16 @@
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" s="11" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B352" s="11" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C352" s="11" t="s">
         <v>44</v>
       </c>
       <c r="D352" s="11" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E352" s="11">
         <v>7</v>
@@ -11822,16 +11825,16 @@
     </row>
     <row r="353" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A353" s="10" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B353" s="10" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C353" s="10" t="s">
         <v>39</v>
       </c>
       <c r="D353" s="10" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E353" s="10"/>
       <c r="F353" s="10"/>
@@ -11843,22 +11846,22 @@
     </row>
     <row r="354" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A354" s="11" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C354" s="11" t="s">
         <v>39</v>
       </c>
       <c r="D354" s="11" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E354" s="11">
         <v>80</v>
       </c>
       <c r="F354" s="11" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G354" s="12"/>
       <c r="H354" s="12"/>
@@ -11868,16 +11871,16 @@
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" s="11" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B355" s="11" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C355" s="11" t="s">
         <v>39</v>
       </c>
       <c r="D355" s="11" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E355" s="11">
         <v>40</v>
@@ -11893,22 +11896,22 @@
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356" s="11" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C356" s="11" t="s">
         <v>39</v>
       </c>
       <c r="D356" s="11" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E356" s="11">
         <v>60</v>
       </c>
       <c r="F356" s="11" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G356" s="12"/>
       <c r="H356" s="12"/>
@@ -12257,10 +12260,10 @@
         <v>27</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>35</v>
@@ -12268,91 +12271,91 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
@@ -12384,664 +12387,664 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>746</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>745</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>743</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B9" s="15" t="s">
+        <v>755</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>754</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>753</v>
-      </c>
       <c r="D9" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>768</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="D15" s="15" t="s">
         <v>767</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>765</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B20" s="15" t="s">
+        <v>777</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>775</v>
-      </c>
       <c r="D20" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
+        <v>771</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>780</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>770</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>779</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>769</v>
-      </c>
       <c r="D22" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B24" s="15" t="s">
+        <v>784</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>783</v>
       </c>
-      <c r="C24" s="15" t="s">
-        <v>782</v>
-      </c>
       <c r="D24" s="15" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B30" s="15" t="s">
+        <v>793</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>792</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>791</v>
-      </c>
       <c r="D30" s="15" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B33" s="15" t="s">
+        <v>798</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>796</v>
+      </c>
+      <c r="D33" s="15" t="s">
         <v>797</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>795</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B36" s="15" t="s">
+        <v>805</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>806</v>
+      </c>
+      <c r="D36" s="15" t="s">
         <v>804</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>805</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B40" s="15" t="s">
+        <v>813</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>811</v>
+      </c>
+      <c r="D40" s="15" t="s">
         <v>812</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>810</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C57" s="15">
         <v>6</v>
@@ -13049,10 +13052,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
+        <v>831</v>
+      </c>
+      <c r="B58" s="15" t="s">
         <v>830</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>829</v>
       </c>
       <c r="C58" s="15">
         <v>6</v>
@@ -13060,10 +13063,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C59" s="15">
         <v>6</v>
@@ -13071,10 +13074,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C60" s="15">
         <v>6</v>
@@ -13082,10 +13085,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C61" s="15">
         <v>6</v>
@@ -13093,10 +13096,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C62" s="15">
         <v>20</v>
@@ -13104,10 +13107,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
+        <v>837</v>
+      </c>
+      <c r="B63" s="15" t="s">
         <v>836</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>835</v>
       </c>
       <c r="C63" s="15">
         <v>20</v>
@@ -13115,10 +13118,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C64" s="15">
         <v>16</v>
@@ -13126,10 +13129,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C65" s="15">
         <v>12</v>
@@ -13137,10 +13140,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="15" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C66" s="15">
         <v>14</v>
@@ -13148,10 +13151,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C67" s="15">
         <v>14</v>
@@ -13159,10 +13162,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C68" s="15">
         <v>4</v>
@@ -13170,10 +13173,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
+        <v>844</v>
+      </c>
+      <c r="B69" s="15" t="s">
         <v>843</v>
-      </c>
-      <c r="B69" s="15" t="s">
-        <v>842</v>
       </c>
       <c r="C69" s="15">
         <v>4</v>
@@ -13181,10 +13184,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C70" s="15">
         <v>3</v>
@@ -13192,10 +13195,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
+        <v>847</v>
+      </c>
+      <c r="B71" s="15" t="s">
         <v>846</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>845</v>
       </c>
       <c r="C71" s="15">
         <v>3</v>
